--- a/real_estate_forms/001_home_seller_s_questions_we_are_so_excited_to_work_with_you_and_help_you_this_this_property_sold_we--real_estate_forms.xlsx
+++ b/real_estate_forms/001_home_seller_s_questions_we_are_so_excited_to_work_with_you_and_help_you_this_this_property_sold_we--real_estate_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>We</t>
+          <t>We (2)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>real_estate_forms</t>
+          <t>real_estate_forms_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Real Estate Forms</t>
+          <t>Real Estate Forms 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -924,12 +924,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>form_that_realtors_use</t>
+          <t>form_that_realtors_use_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Form That Realtors Use</t>
+          <t>Form That Realtors Use 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>when_listing_a_home_for_sale</t>
+          <t>when_listing_a_home_for_sale_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>When Listing A Home For Sale</t>
+          <t>When Listing A Home For Sale 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -993,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>real_estate_forms</t>
+          <t>real_estate_forms_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Real Estate Forms</t>
+          <t>Real Estate Forms 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>help_you</t>
+          <t>help_you_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Help You</t>
+          <t>Help You 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>this_property</t>
+          <t>this_property_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>This Property</t>
+          <t>This Property 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
